--- a/static/scripts/SDWAN Installation Tracker Master User Data.xlsx
+++ b/static/scripts/SDWAN Installation Tracker Master User Data.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CORE_CONTENT\Downloads__Replica\D_Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CORE_CONTENT\CODE\dir_root_ITrack\static\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB0F8D0-8F36-43F0-96A6-8334CC347673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
